--- a/scrp-baseline/data/scrp-baseline-training-bohol-hilongos.xlsx
+++ b/scrp-baseline/data/scrp-baseline-training-bohol-hilongos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\viser\OneDrive\Dokumen\Github repository\data-consultation-2026\scrp-baseline\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E135A975-8A85-430A-ACFE-A348E387D773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C2EE6E8-50E0-44C4-B58B-AAB46C134B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33210" yWindow="780" windowWidth="21600" windowHeight="11835" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16475,10 +16475,7 @@
       <c r="S28" s="4">
         <v>750</v>
       </c>
-      <c r="T28" s="5">
-        <f>S28*O28*N28</f>
-        <v>22500</v>
-      </c>
+      <c r="T28" s="5"/>
       <c r="U28" s="1">
         <v>0</v>
       </c>
@@ -16531,14 +16528,11 @@
       </c>
       <c r="P29" s="13"/>
       <c r="Q29" s="13"/>
-      <c r="R29" s="13"/>
+      <c r="R29" s="16"/>
       <c r="S29" s="4">
         <v>1020</v>
       </c>
-      <c r="T29" s="5">
-        <f t="shared" ref="T29:T46" si="1">S29*O29*N29</f>
-        <v>816000</v>
-      </c>
+      <c r="T29" s="5"/>
       <c r="U29" s="1">
         <v>1</v>
       </c>
@@ -16597,14 +16591,11 @@
       </c>
       <c r="P30" s="13"/>
       <c r="Q30" s="13"/>
-      <c r="R30" s="13"/>
+      <c r="R30" s="16"/>
       <c r="S30" s="4">
         <v>750</v>
       </c>
-      <c r="T30" s="5">
-        <f t="shared" si="1"/>
-        <v>60000</v>
-      </c>
+      <c r="T30" s="5"/>
       <c r="U30" s="1">
         <v>1</v>
       </c>
@@ -16663,14 +16654,11 @@
       </c>
       <c r="P31" s="13"/>
       <c r="Q31" s="13"/>
-      <c r="R31" s="13"/>
+      <c r="R31" s="16"/>
       <c r="S31" s="4">
         <v>750</v>
       </c>
-      <c r="T31" s="5">
-        <f t="shared" si="1"/>
-        <v>105000</v>
-      </c>
+      <c r="T31" s="5"/>
       <c r="U31" s="1">
         <v>1</v>
       </c>
@@ -16727,14 +16715,11 @@
       </c>
       <c r="P32" s="13"/>
       <c r="Q32" s="13"/>
-      <c r="R32" s="13"/>
+      <c r="R32" s="16"/>
       <c r="S32" s="4">
         <v>750</v>
       </c>
-      <c r="T32" s="5">
-        <f t="shared" si="1"/>
-        <v>60000</v>
-      </c>
+      <c r="T32" s="5"/>
       <c r="U32" s="1">
         <v>1</v>
       </c>
@@ -16790,14 +16775,11 @@
       </c>
       <c r="P33" s="13"/>
       <c r="Q33" s="13"/>
-      <c r="R33" s="13"/>
+      <c r="R33" s="16"/>
       <c r="S33" s="4">
         <v>750</v>
       </c>
-      <c r="T33" s="5">
-        <f t="shared" si="1"/>
-        <v>30000</v>
-      </c>
+      <c r="T33" s="5"/>
       <c r="U33" s="1">
         <v>1</v>
       </c>
@@ -16856,14 +16838,11 @@
       </c>
       <c r="P34" s="13"/>
       <c r="Q34" s="13"/>
-      <c r="R34" s="13"/>
+      <c r="R34" s="16"/>
       <c r="S34" s="4">
         <v>750</v>
       </c>
-      <c r="T34" s="5">
-        <f t="shared" si="1"/>
-        <v>30000</v>
-      </c>
+      <c r="T34" s="5"/>
       <c r="U34" s="1">
         <v>1</v>
       </c>
@@ -16919,14 +16898,11 @@
       </c>
       <c r="P35" s="13"/>
       <c r="Q35" s="13"/>
-      <c r="R35" s="13"/>
+      <c r="R35" s="16"/>
       <c r="S35" s="4">
         <v>750</v>
       </c>
-      <c r="T35" s="5">
-        <f t="shared" si="1"/>
-        <v>150000</v>
-      </c>
+      <c r="T35" s="5"/>
       <c r="U35" s="1">
         <v>1</v>
       </c>
@@ -16985,14 +16961,11 @@
       </c>
       <c r="P36" s="13"/>
       <c r="Q36" s="13"/>
-      <c r="R36" s="13"/>
+      <c r="R36" s="16"/>
       <c r="S36" s="4">
         <v>750</v>
       </c>
-      <c r="T36" s="5">
-        <f t="shared" si="1"/>
-        <v>45000</v>
-      </c>
+      <c r="T36" s="5"/>
       <c r="U36" s="1">
         <v>1</v>
       </c>
@@ -17051,14 +17024,11 @@
       </c>
       <c r="P37" s="13"/>
       <c r="Q37" s="13"/>
-      <c r="R37" s="13"/>
+      <c r="R37" s="16"/>
       <c r="S37" s="4">
         <v>600</v>
       </c>
-      <c r="T37" s="5">
-        <f t="shared" si="1"/>
-        <v>48000</v>
-      </c>
+      <c r="T37" s="5"/>
       <c r="U37" s="1">
         <v>1</v>
       </c>
@@ -17117,14 +17087,11 @@
       </c>
       <c r="P38" s="13"/>
       <c r="Q38" s="13"/>
-      <c r="R38" s="13"/>
+      <c r="R38" s="16"/>
       <c r="S38" s="4">
         <v>600</v>
       </c>
-      <c r="T38" s="5">
-        <f t="shared" si="1"/>
-        <v>72000</v>
-      </c>
+      <c r="T38" s="5"/>
       <c r="U38" s="1">
         <v>1</v>
       </c>
@@ -17183,14 +17150,11 @@
       </c>
       <c r="P39" s="13"/>
       <c r="Q39" s="13"/>
-      <c r="R39" s="13"/>
+      <c r="R39" s="16"/>
       <c r="S39" s="4">
         <v>750</v>
       </c>
-      <c r="T39" s="5">
-        <f t="shared" si="1"/>
-        <v>75000</v>
-      </c>
+      <c r="T39" s="5"/>
       <c r="U39" s="1">
         <v>0</v>
       </c>
@@ -17246,14 +17210,11 @@
       </c>
       <c r="P40" s="13"/>
       <c r="Q40" s="13"/>
-      <c r="R40" s="13"/>
+      <c r="R40" s="16"/>
       <c r="S40" s="4">
         <v>750</v>
       </c>
-      <c r="T40" s="5">
-        <f t="shared" si="1"/>
-        <v>52500</v>
-      </c>
+      <c r="T40" s="5"/>
       <c r="U40" s="1">
         <v>0</v>
       </c>
@@ -17309,14 +17270,11 @@
       </c>
       <c r="P41" s="13"/>
       <c r="Q41" s="13"/>
-      <c r="R41" s="13"/>
+      <c r="R41" s="16"/>
       <c r="S41" s="4">
         <v>800</v>
       </c>
-      <c r="T41" s="5">
-        <f t="shared" si="1"/>
-        <v>176000</v>
-      </c>
+      <c r="T41" s="5"/>
       <c r="U41" s="1">
         <v>0</v>
       </c>
@@ -17372,14 +17330,11 @@
       </c>
       <c r="P42" s="13"/>
       <c r="Q42" s="13"/>
-      <c r="R42" s="13"/>
+      <c r="R42" s="16"/>
       <c r="S42" s="4">
         <v>750</v>
       </c>
-      <c r="T42" s="5">
-        <f t="shared" si="1"/>
-        <v>75000</v>
-      </c>
+      <c r="T42" s="5"/>
       <c r="U42" s="1">
         <v>1</v>
       </c>
@@ -17435,14 +17390,11 @@
       </c>
       <c r="P43" s="13"/>
       <c r="Q43" s="13"/>
-      <c r="R43" s="13"/>
+      <c r="R43" s="16"/>
       <c r="S43" s="4">
         <v>750</v>
       </c>
-      <c r="T43" s="5">
-        <f t="shared" si="1"/>
-        <v>150000</v>
-      </c>
+      <c r="T43" s="5"/>
       <c r="U43" s="1">
         <v>1</v>
       </c>
@@ -17501,14 +17453,11 @@
       </c>
       <c r="P44" s="13"/>
       <c r="Q44" s="13"/>
-      <c r="R44" s="13"/>
+      <c r="R44" s="16"/>
       <c r="S44" s="4">
         <v>1020</v>
       </c>
-      <c r="T44" s="5">
-        <f t="shared" si="1"/>
-        <v>57120</v>
-      </c>
+      <c r="T44" s="5"/>
       <c r="U44" s="1">
         <v>1</v>
       </c>
@@ -17567,14 +17516,11 @@
       </c>
       <c r="P45" s="13"/>
       <c r="Q45" s="13"/>
-      <c r="R45" s="13"/>
+      <c r="R45" s="16"/>
       <c r="S45" s="4">
         <v>750</v>
       </c>
-      <c r="T45" s="5">
-        <f t="shared" si="1"/>
-        <v>27000</v>
-      </c>
+      <c r="T45" s="5"/>
       <c r="U45" s="1">
         <v>1</v>
       </c>
@@ -17633,14 +17579,11 @@
       </c>
       <c r="P46" s="13"/>
       <c r="Q46" s="13"/>
-      <c r="R46" s="13"/>
+      <c r="R46" s="16"/>
       <c r="S46" s="4">
         <v>750</v>
       </c>
-      <c r="T46" s="5">
-        <f t="shared" si="1"/>
-        <v>25500</v>
-      </c>
+      <c r="T46" s="5"/>
       <c r="U46" s="1">
         <v>1</v>
       </c>

--- a/scrp-baseline/data/scrp-baseline-training-bohol-hilongos.xlsx
+++ b/scrp-baseline/data/scrp-baseline-training-bohol-hilongos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\viser\OneDrive\Dokumen\Github repository\data-consultation-2026\scrp-baseline\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C2EE6E8-50E0-44C4-B58B-AAB46C134B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE02B81A-2E75-478B-B1D7-D57AA1B5C9D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33210" yWindow="780" windowWidth="21600" windowHeight="11835" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bohol" sheetId="1" r:id="rId1"/>
@@ -513,7 +513,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -545,7 +545,6 @@
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15248,7 +15247,7 @@
       <c r="H9" s="1">
         <v>6</v>
       </c>
-      <c r="K9" s="17">
+      <c r="K9">
         <v>1</v>
       </c>
       <c r="L9" s="1">
@@ -15521,7 +15520,7 @@
         <v>2</v>
       </c>
       <c r="O13" s="1">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="P13" s="13">
         <v>1</v>
@@ -15534,8 +15533,8 @@
       </c>
       <c r="S13" s="4"/>
       <c r="T13" s="4">
-        <f t="shared" si="0"/>
-        <v>2080</v>
+        <f>((Q13*R13)*O13)*N13</f>
+        <v>22880</v>
       </c>
       <c r="U13" s="1">
         <v>1</v>
@@ -16042,7 +16041,7 @@
       <c r="H21" s="1">
         <v>2</v>
       </c>
-      <c r="K21" s="17">
+      <c r="K21">
         <v>0.5</v>
       </c>
       <c r="N21" s="1">
@@ -16475,7 +16474,10 @@
       <c r="S28" s="4">
         <v>750</v>
       </c>
-      <c r="T28" s="5"/>
+      <c r="T28" s="5">
+        <f>S28*O27*N27</f>
+        <v>45000</v>
+      </c>
       <c r="U28" s="1">
         <v>0</v>
       </c>
@@ -16532,7 +16534,10 @@
       <c r="S29" s="4">
         <v>1020</v>
       </c>
-      <c r="T29" s="5"/>
+      <c r="T29" s="5">
+        <f t="shared" ref="T29:T46" si="1">S29*O28*N28</f>
+        <v>30600</v>
+      </c>
       <c r="U29" s="1">
         <v>1</v>
       </c>
@@ -16595,7 +16600,10 @@
       <c r="S30" s="4">
         <v>750</v>
       </c>
-      <c r="T30" s="5"/>
+      <c r="T30" s="5">
+        <f t="shared" si="1"/>
+        <v>600000</v>
+      </c>
       <c r="U30" s="1">
         <v>1</v>
       </c>
@@ -16658,7 +16666,10 @@
       <c r="S31" s="4">
         <v>750</v>
       </c>
-      <c r="T31" s="5"/>
+      <c r="T31" s="5">
+        <f t="shared" si="1"/>
+        <v>60000</v>
+      </c>
       <c r="U31" s="1">
         <v>1</v>
       </c>
@@ -16719,7 +16730,10 @@
       <c r="S32" s="4">
         <v>750</v>
       </c>
-      <c r="T32" s="5"/>
+      <c r="T32" s="5">
+        <f t="shared" si="1"/>
+        <v>105000</v>
+      </c>
       <c r="U32" s="1">
         <v>1</v>
       </c>
@@ -16779,7 +16793,10 @@
       <c r="S33" s="4">
         <v>750</v>
       </c>
-      <c r="T33" s="5"/>
+      <c r="T33" s="5">
+        <f t="shared" si="1"/>
+        <v>60000</v>
+      </c>
       <c r="U33" s="1">
         <v>1</v>
       </c>
@@ -16842,7 +16859,10 @@
       <c r="S34" s="4">
         <v>750</v>
       </c>
-      <c r="T34" s="5"/>
+      <c r="T34" s="5">
+        <f t="shared" si="1"/>
+        <v>30000</v>
+      </c>
       <c r="U34" s="1">
         <v>1</v>
       </c>
@@ -16902,7 +16922,10 @@
       <c r="S35" s="4">
         <v>750</v>
       </c>
-      <c r="T35" s="5"/>
+      <c r="T35" s="5">
+        <f t="shared" si="1"/>
+        <v>30000</v>
+      </c>
       <c r="U35" s="1">
         <v>1</v>
       </c>
@@ -16965,7 +16988,10 @@
       <c r="S36" s="4">
         <v>750</v>
       </c>
-      <c r="T36" s="5"/>
+      <c r="T36" s="5">
+        <f t="shared" si="1"/>
+        <v>150000</v>
+      </c>
       <c r="U36" s="1">
         <v>1</v>
       </c>
@@ -17028,7 +17054,10 @@
       <c r="S37" s="4">
         <v>600</v>
       </c>
-      <c r="T37" s="5"/>
+      <c r="T37" s="5">
+        <f t="shared" si="1"/>
+        <v>36000</v>
+      </c>
       <c r="U37" s="1">
         <v>1</v>
       </c>
@@ -17091,7 +17120,10 @@
       <c r="S38" s="4">
         <v>600</v>
       </c>
-      <c r="T38" s="5"/>
+      <c r="T38" s="5">
+        <f t="shared" si="1"/>
+        <v>48000</v>
+      </c>
       <c r="U38" s="1">
         <v>1</v>
       </c>
@@ -17154,7 +17186,10 @@
       <c r="S39" s="4">
         <v>750</v>
       </c>
-      <c r="T39" s="5"/>
+      <c r="T39" s="5">
+        <f t="shared" si="1"/>
+        <v>90000</v>
+      </c>
       <c r="U39" s="1">
         <v>0</v>
       </c>
@@ -17214,7 +17249,10 @@
       <c r="S40" s="4">
         <v>750</v>
       </c>
-      <c r="T40" s="5"/>
+      <c r="T40" s="5">
+        <f t="shared" si="1"/>
+        <v>75000</v>
+      </c>
       <c r="U40" s="1">
         <v>0</v>
       </c>
@@ -17274,7 +17312,10 @@
       <c r="S41" s="4">
         <v>800</v>
       </c>
-      <c r="T41" s="5"/>
+      <c r="T41" s="5">
+        <f t="shared" si="1"/>
+        <v>56000</v>
+      </c>
       <c r="U41" s="1">
         <v>0</v>
       </c>
@@ -17334,7 +17375,10 @@
       <c r="S42" s="4">
         <v>750</v>
       </c>
-      <c r="T42" s="5"/>
+      <c r="T42" s="5">
+        <f t="shared" si="1"/>
+        <v>165000</v>
+      </c>
       <c r="U42" s="1">
         <v>1</v>
       </c>
@@ -17394,7 +17438,10 @@
       <c r="S43" s="4">
         <v>750</v>
       </c>
-      <c r="T43" s="5"/>
+      <c r="T43" s="5">
+        <f t="shared" si="1"/>
+        <v>75000</v>
+      </c>
       <c r="U43" s="1">
         <v>1</v>
       </c>
@@ -17457,7 +17504,10 @@
       <c r="S44" s="4">
         <v>1020</v>
       </c>
-      <c r="T44" s="5"/>
+      <c r="T44" s="5">
+        <f t="shared" si="1"/>
+        <v>204000</v>
+      </c>
       <c r="U44" s="1">
         <v>1</v>
       </c>
@@ -17520,7 +17570,10 @@
       <c r="S45" s="4">
         <v>750</v>
       </c>
-      <c r="T45" s="5"/>
+      <c r="T45" s="5">
+        <f t="shared" si="1"/>
+        <v>42000</v>
+      </c>
       <c r="U45" s="1">
         <v>1</v>
       </c>
@@ -17583,7 +17636,10 @@
       <c r="S46" s="4">
         <v>750</v>
       </c>
-      <c r="T46" s="5"/>
+      <c r="T46" s="5">
+        <f t="shared" si="1"/>
+        <v>27000</v>
+      </c>
       <c r="U46" s="1">
         <v>1</v>
       </c>
